--- a/merchant_forms/009_product_order_form_full_width_and_responsive--merchant_forms.xlsx
+++ b/merchant_forms/009_product_order_form_full_width_and_responsive--merchant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>product_order_form_full_width_and_responsive</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Product Order Form Full Width And Responsive</t>
+          <t>Product Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,131 +543,127 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_tab_navigation</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Form Tab Navigation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Form tabs navigation is positioned to the right side of the form with cool callout design</t>
-        </is>
-      </c>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_tabs_navigation</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Form tab navigation</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_tab_position</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form tab position</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_tab_position_2</t>
+          <t>delivery_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Form tab position</t>
+          <t>Delivery Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_positioned_to_the_side_of_the_form</t>
+          <t>delivery_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Form positioned to the right side of the form</t>
+          <t>Delivery Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_positioned_to_the_right_side_of_the_form</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form positioned to the right side of the form</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,21 +676,113 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>product_order_form_full_width_and_responsive</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Product Order Form Full Width And Responsive</t>
+          <t>Special Requests</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>delivery_method</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Delivery Method</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>select_multiple_options</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Select Multiple Options</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>confirm_select_multiple</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Confirm Select Multiple Options</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -711,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -739,170 +827,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_tabs_navigation_choices</t>
+          <t>delivery_method_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>in-store_pickup</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>In-store pickup</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_tabs_navigation_choices</t>
+          <t>delivery_method_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Delivery</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_tab_position_choices</t>
+          <t>delivery_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pickup</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_tab_position_choices</t>
+          <t>select_multiple_options_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_tab_position_2_choices</t>
+          <t>select_multiple_options_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_tab_position_2_choices</t>
+          <t>select_multiple_options_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_positioned_to_the_right_side_of_the_form_choices</t>
+          <t>confirm_select_multiple_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_positioned_to_the_right_side_of_the_form_choices</t>
+          <t>confirm_select_multiple_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>product_order_form_full_width_and_responsive_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>product_order_form_full_width_and_responsive_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
